--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_llama3.2-vision-binary_random_noise.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_llama3.2-vision-binary_random_noise.xlsx
@@ -752,6 +752,18 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:U2">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
